--- a/READING/18_25_12.xlsx
+++ b/READING/18_25_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C1A7D6-29C4-4AE3-8488-0696EE822F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32122443-2F4F-442E-A181-09ADDEFA0543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1005" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t>Fre</t>
   </si>
@@ -732,6 +732,225 @@
   </si>
   <si>
     <t>通过…;因为…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひと言で</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用一句话来说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悩み</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烦恼；忧虑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なやみ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">どうにも </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无论如何也…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ならない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不变成（预想的样子）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～しだい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取决于…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なんとか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设法、总算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しようとする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>想要/试图去做某事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かえって</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反而、相反地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ますます</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>越来越…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なかで</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在…中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>てゆく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同"ていく"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向き合う</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面对</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>つながる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接，导致，关联</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">達する </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>达到</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ようになる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变得…;开始能够…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>によって</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>てみると</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尝试后(发现)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>示す</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示；表明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しめす</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集団</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>群体；团体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅうだん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あてはめる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>适用；应用；适合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>付き合う</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交往；陪伴；交际</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ではないかと思う</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我想是不是…呢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>よりよき</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>同“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よりよい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>”</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1143,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
@@ -1978,6 +2197,268 @@
       </c>
       <c r="C71" s="2" t="s">
         <v>157</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A72" s="2">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A73" s="2">
+        <v>0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A74" s="2">
+        <v>0</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A75" s="2">
+        <v>0</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A76" s="2">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A77" s="2">
+        <v>0</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A78" s="2">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A79" s="2">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A80" s="2">
+        <v>0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A81" s="2">
+        <v>0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A82" s="2">
+        <v>0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A83" s="2">
+        <v>0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A84" s="2">
+        <v>0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A85" s="2">
+        <v>0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A86" s="2">
+        <v>0</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A87" s="2">
+        <v>0</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A88" s="2">
+        <v>0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A89" s="2">
+        <v>0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A90" s="2">
+        <v>0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A91" s="2">
+        <v>0</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A92" s="2">
+        <v>0</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A93" s="2">
+        <v>0</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A94" s="2">
+        <v>0</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/READING/18_25_12.xlsx
+++ b/READING/18_25_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32122443-2F4F-442E-A181-09ADDEFA0543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61356B2-9124-46E4-A634-A66851A12BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1005" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17520" yWindow="1005" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="257">
   <si>
     <t>Fre</t>
   </si>
@@ -951,6 +951,206 @@
       </rPr>
       <t>”</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛を歌にする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>把爱做成歌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>だが</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>但是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行動</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行为</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>こうどう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～んだ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带有强烈的主观结论色彩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～ようにする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>努力做到</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生かす</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发挥作用;使…有效利用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我慢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>がまん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忍耐；克制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>見守る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>みまもる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>守护；看护</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ようとする-&gt;试图…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>りてん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优点；好处</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～につれて</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随着；伴随着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感じ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんじ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感觉；印象；氛围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～といったこと</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诸如此类的东西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>明らかに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清楚地；明确地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>発する</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>はっする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发出；发表；出发；发生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>セリフ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぴったり</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紧密地;紧紧地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ですが、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恋に落ちる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>こいにおちる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坠入爱河；陷入恋情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当てはまる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>符合；适合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いっぱんてき</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普遍的；普通的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～にしたがって</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按照；根据</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1362,14 +1562,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.875" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2459,6 +2659,264 @@
       </c>
       <c r="C94" s="2" t="s">
         <v>206</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A95" s="2">
+        <v>0</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A96" s="2">
+        <v>0</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A97" s="2">
+        <v>0</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A98" s="2">
+        <v>0</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A99" s="2">
+        <v>0</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A100" s="2">
+        <v>0</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A101" s="2">
+        <v>0</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A102" s="2">
+        <v>0</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A103" s="2">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A104" s="2">
+        <v>0</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A105" s="2">
+        <v>0</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A106" s="2">
+        <v>0</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A107" s="2">
+        <v>0</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A108" s="2">
+        <v>0</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A109" s="2">
+        <v>0</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A110" s="2">
+        <v>0</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A111" s="2">
+        <v>0</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A112" s="2">
+        <v>0</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A113" s="2">
+        <v>0</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A114" s="2">
+        <v>0</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A115" s="2">
+        <v>0</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/READING/18_25_12.xlsx
+++ b/READING/18_25_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61356B2-9124-46E4-A634-A66851A12BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AEEEA4-DBCC-41EE-B23D-B5AD514F0615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17520" yWindow="1005" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15405" yWindow="1005" windowWidth="22995" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
